--- a/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
+++ b/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>CODE-001~005/015/016</t>
+          <t>CODE-001~005/013~016</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>TBX-001~003/013</t>
+          <t>TBX-001~004/013</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr"/>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>CST-002~004</t>
+          <t>CST-002~004, ERP-028</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr"/>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="H37" s="22" t="inlineStr">
         <is>
-          <t>ERP-002/003</t>
+          <t>ERP-002/003/016</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H38" s="22" t="inlineStr">
         <is>
-          <t>ERP-004/005/009</t>
+          <t>ERP-004/005/009/010</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="H40" s="22" t="inlineStr">
         <is>
-          <t>ERP-006/008/023~025/030</t>
+          <t>ERP-006/008/023~025/030, DWG-021</t>
         </is>
       </c>
       <c r="I40" s="22" t="inlineStr"/>

--- a/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
+++ b/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 + 수량 + Slot 매핑(match_condition), Part List Running Test 검증</t>
+          <t>Mother-Child 관계 + 수량 + Slot 매핑 테이블, Part List Running Test 검증</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">

--- a/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
+++ b/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>SYS-013~020</t>
+          <t>SYS-013~021</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr"/>
@@ -3842,20 +3842,24 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>다국어</t>
+          <t>다국어 (i18n)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>한국어 기본, 다국어 확장 구조(i18n)</t>
+          <t>한국어 기본 + 영어·일본어·중국어 지원 — UI 리소스 번들 + 데이터 라벨 번역(sys_translation), 로케일별 날짜·숫자·통화 포맷, 번역 누락 시 KO 폴백</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>영어 1차 (협의)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr"/>
+          <t>4개 로케일(ko/en/ja/zh) 전환 100%</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>확정 (2026-07-07)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">

--- a/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
+++ b/edim-ai-blueprint/docs/02_요구사항/EDIM_요구사항정의서.xlsx
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2</t>
         </is>
       </c>
     </row>
@@ -671,70 +671,82 @@
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>개정</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>EDIM Tool System EP2.pptx (78슬라이드) 분석 → 기능정의서 v0.2(178기능)·메뉴정의서 v0.3(97메뉴)·컴포넌트정의서에서 도출</t>
+          <t>v0.2 (2026-07-25) — REQ-F-042 다국어 라벨 검수 항목 추가 (변경관리대장 No.2)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>요구사항 수</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>기능 50 · 비기능 22 · 인터페이스 8</t>
+          <t>EDIM Tool System EP2.pptx (78슬라이드) 분석 → 기능정의서 v0.2(178기능)·메뉴정의서 v0.3(97메뉴)·컴포넌트정의서에서 도출</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ID 체계</t>
+          <t>요구사항 수</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>REQ-F-xxx(기능) / REQ-N-xxx(비기능) / REQ-I-xxx(인터페이스)</t>
+          <t>기능 50 · 비기능 22 · 인터페이스 8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>중요도</t>
+          <t>ID 체계</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>필수 = v1 범위 / 선택 = 협의·후순위</t>
+          <t>REQ-F-xxx(기능) / REQ-N-xxx(비기능) / REQ-I-xxx(인터페이스)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>중요도</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>P1 RCCS코어 / P2 설계·Run / P3 원가·문서 / P4 Toolbox·AI / P5 ERP·모바일</t>
+          <t>필수 = v1 범위 / 선택 = 협의·후순위</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>P1 RCCS코어 / P2 설계·Run / P3 원가·문서 / P4 Toolbox·AI / P5 ERP·모바일</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>관련 기능 ID → EDIM_기능정의서.xlsx, 화면 → EDIM_화면설계서.html, DB → EDIM_DB정의서.xlsx</t>
         </is>
@@ -2955,7 +2967,7 @@
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>전후 공정·일정·이상 경고(시간/자금)·손익·자금 흐름 집계, 회사 마스터, 업체/Project 평가</t>
+          <t>전후 공정·일정·이상 경고(시간/자금)·손익·자금 흐름 집계, 회사 마스터, 업체/Project 평가, 다국어(EN/JA/ZH) 라벨 검수</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2973,7 +2985,11 @@
           <t>ERP-013~015</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr"/>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>다국어 라벨 검수 항목 추가 — 변경관리대장 No.2 (2026-07-25)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
